--- a/Assets/Data/TestDialogue.xlsx
+++ b/Assets/Data/TestDialogue.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>flow</t>
   </si>
@@ -58,169 +58,19 @@
     <t>ambient</t>
   </si>
   <si>
-    <t>jump:不存在</t>
-  </si>
-  <si>
-    <t>小明</t>
-  </si>
-  <si>
-    <t>早上好！</t>
-  </si>
-  <si>
-    <t>微笑</t>
-  </si>
-  <si>
-    <t>play:小明入场，se:whoosh:vol(0.3)</t>
-  </si>
-  <si>
-    <t>happy</t>
-  </si>
-  <si>
-    <t>wind_loop:in(2):vol(0.3)</t>
-  </si>
-  <si>
-    <t>今天的天气很不错呢。</t>
-  </si>
-  <si>
-    <t>可是，昨晚做了一个很奇怪的梦。</t>
-  </si>
-  <si>
-    <t>tenseness:out(3):in(1):vol(0.4)</t>
-  </si>
-  <si>
-    <t>wind_loop:out(3):stop</t>
-  </si>
-  <si>
-    <t>我梦见自己，{w}变成了一只鸟。</t>
-  </si>
-  <si>
-    <t>小明_疑惑</t>
-  </si>
-  <si>
-    <t>shake：1,flash，play:推镜头</t>
-  </si>
-  <si>
-    <t>bird_loop</t>
-  </si>
-  <si>
-    <t>wait:1</t>
-  </si>
-  <si>
-    <t>shake</t>
-  </si>
-  <si>
-    <t>jump:风吹</t>
-  </si>
-  <si>
-    <t>其实我一直想告诉你——{nw}</t>
-  </si>
-  <si>
-    <t>小明_严肃</t>
-  </si>
-  <si>
-    <t>bird_loop:stop</t>
-  </si>
-  <si>
-    <t>其实我们都是假的！</t>
-  </si>
-  <si>
-    <t>label:风吹</t>
-  </si>
-  <si>
-    <t>{clear}</t>
-  </si>
-  <si>
-    <t>一阵风吹过</t>
-  </si>
-  <si>
-    <t>wind_loop：vol（0.3）,bird_loop</t>
-  </si>
-  <si>
-    <t>……算了，不说这个了，我先走了。</t>
-  </si>
-  <si>
-    <t>Sub</t>
-  </si>
-  <si>
-    <t>微笑:left</t>
-  </si>
-  <si>
-    <t>se:whoosh:full</t>
-  </si>
-  <si>
-    <t>happy:in(0.1)</t>
-  </si>
-  <si>
-    <t>你？{w}等等，{w}你是什么时候...</t>
-  </si>
-  <si>
-    <t>小明_疑惑:pos(1440,540)</t>
-  </si>
-  <si>
-    <t>我们都在啊。{w}是个很好的日子，{w}不是吗？</t>
-  </si>
-  <si>
-    <t>我怎么回答？</t>
-  </si>
-  <si>
-    <t>option:是&gt;分支A</t>
-  </si>
-  <si>
-    <t>option:不是&gt;分支B</t>
-  </si>
-  <si>
-    <t>label:分支A</t>
-  </si>
-  <si>
-    <t>Sub笑</t>
-  </si>
-  <si>
-    <t>Sub_微笑</t>
-  </si>
-  <si>
-    <t>jump:汇合</t>
-  </si>
-  <si>
-    <t>我也这么觉得。</t>
-  </si>
-  <si>
-    <t>label:分支B</t>
-  </si>
-  <si>
-    <t>……</t>
-  </si>
-  <si>
-    <t>tenseness:out(0.5):gap(2):vol(0.4)</t>
-  </si>
-  <si>
-    <t>我知道了。</t>
-  </si>
-  <si>
-    <t>至少，我们{nw}</t>
-  </si>
-  <si>
-    <t>label:汇合</t>
-  </si>
-  <si>
-    <t>可是...我要走了</t>
-  </si>
-  <si>
-    <t>伤心</t>
-  </si>
-  <si>
-    <t>我也是</t>
-  </si>
-  <si>
-    <t>end</t>
-  </si>
-  <si>
-    <t>两人离开了。</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>可他们也没有来过。</t>
+    <t>Cus</t>
+  </si>
+  <si>
+    <t>Fly</t>
+  </si>
+  <si>
+    <t>Fly/BG/room</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>room</t>
   </si>
 </sst>
 </file>
@@ -1154,18 +1004,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="21.875" customWidth="1"/>
-    <col min="2" max="2" width="14.25" customWidth="1"/>
-    <col min="3" max="3" width="41.875" customWidth="1"/>
-    <col min="4" max="4" width="21.875" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="13.625" customWidth="1"/>
-    <col min="7" max="7" width="38" customWidth="1"/>
-    <col min="8" max="8" width="36" customWidth="1"/>
-    <col min="9" max="9" width="33.625" customWidth="1"/>
+    <col min="2" max="2" width="12.25" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="16.25" customWidth="1"/>
+    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="6" max="6" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1175,7 +1021,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -1198,264 +1044,24 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="C3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:9">
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="B6" s="1"/>
-      <c r="G6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="B7" s="1"/>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="B9" s="1"/>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" t="s">
-        <v>52</v>
-      </c>
-      <c r="H21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="C22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" t="s">
-        <v>58</v>
-      </c>
-      <c r="H24" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="B25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" t="s">
-        <v>61</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="C27" t="s">
-        <v>63</v>
+    <row r="4" spans="1:9">
+      <c r="C4" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
